--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -1,41 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2CB2A59-85B8-4A9D-A809-9EB987D18315}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5F1865F-CF7B-4EEE-9993-C539962AEF73}"/>
   <bookViews>
-    <workbookView xWindow="14028" yWindow="2052" windowWidth="8904" windowHeight="10116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="900" windowWidth="8808" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="251230" sheetId="23" r:id="rId1"/>
-    <sheet name="251128" sheetId="22" r:id="rId2"/>
-    <sheet name="251031" sheetId="21" r:id="rId3"/>
-    <sheet name="250926" sheetId="20" r:id="rId4"/>
-    <sheet name="250919" sheetId="19" r:id="rId5"/>
-    <sheet name="250912" sheetId="18" r:id="rId6"/>
-    <sheet name="250905" sheetId="17" r:id="rId7"/>
-    <sheet name="250815" sheetId="16" r:id="rId8"/>
-    <sheet name="250808" sheetId="15" r:id="rId9"/>
-    <sheet name="250718" sheetId="14" r:id="rId10"/>
-    <sheet name="250704" sheetId="13" r:id="rId11"/>
-    <sheet name="250627" sheetId="12" r:id="rId12"/>
-    <sheet name="250620" sheetId="11" r:id="rId13"/>
-    <sheet name="250613" sheetId="10" r:id="rId14"/>
-    <sheet name="250530" sheetId="9" r:id="rId15"/>
-    <sheet name="250523" sheetId="8" r:id="rId16"/>
-    <sheet name="250516" sheetId="7" r:id="rId17"/>
-    <sheet name="250509" sheetId="6" r:id="rId18"/>
-    <sheet name="250502" sheetId="5" r:id="rId19"/>
-    <sheet name="250411" sheetId="4" r:id="rId20"/>
-    <sheet name="250221" sheetId="3" r:id="rId21"/>
-    <sheet name="250131" sheetId="2" r:id="rId22"/>
-    <sheet name="1230" sheetId="1" r:id="rId23"/>
+    <sheet name="260130" sheetId="24" r:id="rId1"/>
+    <sheet name="251230" sheetId="23" r:id="rId2"/>
+    <sheet name="251128" sheetId="22" r:id="rId3"/>
+    <sheet name="251031" sheetId="21" r:id="rId4"/>
+    <sheet name="250926" sheetId="20" r:id="rId5"/>
+    <sheet name="250919" sheetId="19" r:id="rId6"/>
+    <sheet name="250912" sheetId="18" r:id="rId7"/>
+    <sheet name="250905" sheetId="17" r:id="rId8"/>
+    <sheet name="250815" sheetId="16" r:id="rId9"/>
+    <sheet name="250808" sheetId="15" r:id="rId10"/>
+    <sheet name="250718" sheetId="14" r:id="rId11"/>
+    <sheet name="250704" sheetId="13" r:id="rId12"/>
+    <sheet name="250627" sheetId="12" r:id="rId13"/>
+    <sheet name="250620" sheetId="11" r:id="rId14"/>
+    <sheet name="250613" sheetId="10" r:id="rId15"/>
+    <sheet name="250530" sheetId="9" r:id="rId16"/>
+    <sheet name="250523" sheetId="8" r:id="rId17"/>
+    <sheet name="250516" sheetId="7" r:id="rId18"/>
+    <sheet name="250509" sheetId="6" r:id="rId19"/>
+    <sheet name="250502" sheetId="5" r:id="rId20"/>
+    <sheet name="250411" sheetId="4" r:id="rId21"/>
+    <sheet name="250221" sheetId="3" r:id="rId22"/>
+    <sheet name="250131" sheetId="2" r:id="rId23"/>
+    <sheet name="1230" sheetId="1" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="9">
   <si>
     <t>As end of</t>
   </si>
@@ -193,6 +194,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,6 +496,3592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46052</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1325.62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>5.2354981860328352E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-1012060</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.57756091993380132</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1270445</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.3910866553794059</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-444820</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73726257168429077</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5604140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2727325</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4866625387659837</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1619440</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.31343797781949795</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10770840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4346765</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40356787400054223</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46386</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>2.3713087555403624E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1063500</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.60691662386577638</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1303865</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.40137448052947516</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-447370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74148904431995222</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2814735</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.50225993640415834</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1652290</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.31979600131612052</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4467025</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.41473320558099463</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2470830</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10377630</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4202620</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45863</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1217.1500000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>416540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-284400</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68276756133864691</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1326800</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36942267266222106</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1152920</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.7063422045777582</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5640330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2764120</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.49006352465192637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1802045</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35781484239265327</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10676580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4566165</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.42768049319164003</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45856</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>7.7361287211814803E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>503540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-350840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.69674703102037572</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1314900</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36610933997856077</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1153940</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.70696711267950796</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5727330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2819680</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.49232015616351771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1834700</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.36429883345743358</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10763580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4654380</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.43241932516876358</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5901330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3097650</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10893580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5003995</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5901330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3097650</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10893580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5003995</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3389330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11078080</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5334700</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3389330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11078080</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5334700</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3437705</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11058430</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5421920</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3437705</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11058430</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5421920</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D16" s="5" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6286830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3430330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11258428</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5300498</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D4" s="5" t="e" cm="1">
+        <f t="array" ref="D4">B61632240=C4/B4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6286830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3430330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11258428</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5300498</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3439950</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5183728</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3439950</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5183728</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3447470</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5178568</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3447470</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5178568</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45793</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1195.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.2527458007828689E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-679870</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.36924773113625131</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1443820</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.60651963873135895</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1312520</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66382763503944975</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6198930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3436210</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55432308479043968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1727818</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34753775345472421</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11170528</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5164028</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46229041277189403</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45793</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1195.77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.2527458007828689E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-679870</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.36924773113625131</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1443820</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.60651963873135895</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1312520</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66382763503944975</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6198930</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3436210</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55432308479043968</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1727818</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34753775345472421</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11170528</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5164028</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46229041277189403</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45786</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1210.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>9.975145540376016E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-710950</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.38612775155738283</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1391200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.58441503885738288</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>2091200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1352900</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.64694912012241779</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6312930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3455050</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5472973722186053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4924600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1735475</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35240933273768427</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>265724.25</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.3958544856435038E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11237530</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5190525</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46189198160093897</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45758</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1210.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>9.975145540376016E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-710950</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.38612775155738283</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1391200</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.58441503885738288</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2091200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1352900</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.64694912012241779</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6312930</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3455050</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.5472973722186053</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4924600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1735475</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.35240933273768427</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>265724.25</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.3958544856435038E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11237530</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5190525</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46189198160093897</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45758</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1198.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>6.2303971080750566E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-752850</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.40888427844430081</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1398380</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.58743121193026671</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>2091200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1372640</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.65638867635807197</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6312930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3523870</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55819880784358455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4924600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1799575</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3654256183243309</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>272742</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.5383584453559682E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11237530</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5323445</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.47372020363905593</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -816,2941 +4407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45856</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1206.58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>7.7361287211814803E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>503540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-350840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.69674703102037572</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1314900</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36610933997856077</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1153940</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.70696711267950796</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5727330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2819680</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.49232015616351771</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1834700</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.36429883345743358</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10763580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4654380</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.43241932516876358</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5901330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3097650</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10893580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5003995</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5901330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3097650</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10893580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5003995</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3389330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11078080</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5334700</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3389330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11078080</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5334700</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3437705</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11058430</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5421920</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3437705</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11058430</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5421920</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D16" s="5" t="e">
-        <v>#NAME?</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6286830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3430330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11258428</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5300498</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D4" s="5" t="e" cm="1">
-        <f t="array" ref="D4">B61632240=C4/B4</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6286830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3430330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11258428</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5300498</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3439950</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5183728</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3439950</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5183728</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3447470</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5178568</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3447470</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5178568</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45793</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1195.77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.2527458007828689E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-679870</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.36924773113625131</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1443820</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.60651963873135895</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1312520</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66382763503944975</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6198930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3436210</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55432308479043968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1727818</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34753775345472421</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11170528</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5164028</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46229041277189403</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45793</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1195.77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.2527458007828689E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-679870</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.36924773113625131</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1443820</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.60651963873135895</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1312520</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66382763503944975</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6198930</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3436210</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55432308479043968</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1727818</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34753775345472421</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11170528</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5164028</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46229041277189403</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45786</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1210.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>9.975145540376016E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-710950</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.38612775155738283</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1391200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.58441503885738288</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>2091200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1352900</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.64694912012241779</v>
-      </c>
-      <c r="E18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6312930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3455050</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5472973722186053</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4924600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1735475</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35240933273768427</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>265724.25</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.3958544856435038E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11237530</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5190525</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46189198160093897</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45758</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1210.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>9.975145540376016E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-710950</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.38612775155738283</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1391200</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.58441503885738288</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>2091200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1352900</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.64694912012241779</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6312930</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3455050</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.5472973722186053</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4924600</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1735475</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.35240933273768427</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>265724.25</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.3958544856435038E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11237530</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5190525</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46189198160093897</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45758</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1198.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>6.2303971080750566E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-752850</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.40888427844430081</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1398380</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.58743121193026671</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>2091200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1372640</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.65638867635807197</v>
-      </c>
-      <c r="E18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6312930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3523870</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55819880784358455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4924600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1799575</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3654256183243309</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>272742</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.5383584453559682E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11237530</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5323445</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.47372020363905593</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBF241-CA72-4CB5-8C3F-136F3E8408B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4076,333 +4733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45989</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1256.69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-4.032836960672008E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-1075520</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.61377617987787481</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1365410</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42032014776050486</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-449480</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74498624324593099</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5604140</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2890410</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.51576334638320953</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1747535</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.33823039851355796</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10770840</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4637945</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.43060197719026555</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45961</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1309.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-982080</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.56045197740112995</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1269700</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39085731876250579</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-434590</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.72030695793416644</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5604140</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2686370</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.47935454860156956</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1722405</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.33336655892542627</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>298535.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.7780730446900345E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10770840</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4408775</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40932508513727806</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D4DEBF-7012-4D3C-9A89-43C32C47B6EC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4728,7 +5059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4D270-1B52-4C5B-9E28-60314EA92662}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5054,7 +5385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4C31B2-332E-43CB-8F48-59EA1BD2A5D3}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5380,7 +5711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5710,6 +6041,332 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45989</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1256.69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-4.032836960672008E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-1075520</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.61377617987787481</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1365410</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42032014776050486</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-449480</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74498624324593099</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5604140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2890410</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.51576334638320953</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1747535</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.33823039851355796</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10770840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4637945</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.43060197719026555</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45961</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1309.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-982080</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.56045197740112995</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1269700</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39085731876250579</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-434590</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.72030695793416644</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2686370</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.47935454860156956</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1722405</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.33336655892542627</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>298535.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.7780730446900345E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4408775</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40932508513727806</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FC00D-7E5D-4548-BEF2-5CBFB9DBC724}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6035,7 +6692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6361,7 +7018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6687,7 +7344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7013,7 +7670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7339,7 +7996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7663,330 +8320,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2470830</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10377630</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4202620</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45863</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1217.1500000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>416540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-284400</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.68276756133864691</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1326800</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36942267266222106</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1152920</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.7063422045777582</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5640330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2764120</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.49006352465192637</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1802045</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35781484239265327</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10676580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4566165</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.42768049319164003</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -1,42 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5F1865F-CF7B-4EEE-9993-C539962AEF73}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBED09B0-0CE9-4646-8AED-F3F94F4AF963}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="900" windowWidth="8808" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14412" yWindow="828" windowWidth="8844" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="260130" sheetId="24" r:id="rId1"/>
-    <sheet name="251230" sheetId="23" r:id="rId2"/>
-    <sheet name="251128" sheetId="22" r:id="rId3"/>
-    <sheet name="251031" sheetId="21" r:id="rId4"/>
-    <sheet name="250926" sheetId="20" r:id="rId5"/>
-    <sheet name="250919" sheetId="19" r:id="rId6"/>
-    <sheet name="250912" sheetId="18" r:id="rId7"/>
-    <sheet name="250905" sheetId="17" r:id="rId8"/>
-    <sheet name="250815" sheetId="16" r:id="rId9"/>
-    <sheet name="250808" sheetId="15" r:id="rId10"/>
-    <sheet name="250718" sheetId="14" r:id="rId11"/>
-    <sheet name="250704" sheetId="13" r:id="rId12"/>
-    <sheet name="250627" sheetId="12" r:id="rId13"/>
-    <sheet name="250620" sheetId="11" r:id="rId14"/>
-    <sheet name="250613" sheetId="10" r:id="rId15"/>
-    <sheet name="250530" sheetId="9" r:id="rId16"/>
-    <sheet name="250523" sheetId="8" r:id="rId17"/>
-    <sheet name="250516" sheetId="7" r:id="rId18"/>
-    <sheet name="250509" sheetId="6" r:id="rId19"/>
-    <sheet name="250502" sheetId="5" r:id="rId20"/>
-    <sheet name="250411" sheetId="4" r:id="rId21"/>
-    <sheet name="250221" sheetId="3" r:id="rId22"/>
-    <sheet name="250131" sheetId="2" r:id="rId23"/>
-    <sheet name="1230" sheetId="1" r:id="rId24"/>
+    <sheet name="260227" sheetId="25" r:id="rId1"/>
+    <sheet name="260130" sheetId="24" r:id="rId2"/>
+    <sheet name="251230" sheetId="23" r:id="rId3"/>
+    <sheet name="251128" sheetId="22" r:id="rId4"/>
+    <sheet name="251031" sheetId="21" r:id="rId5"/>
+    <sheet name="250926" sheetId="20" r:id="rId6"/>
+    <sheet name="250919" sheetId="19" r:id="rId7"/>
+    <sheet name="250912" sheetId="18" r:id="rId8"/>
+    <sheet name="250905" sheetId="17" r:id="rId9"/>
+    <sheet name="250815" sheetId="16" r:id="rId10"/>
+    <sheet name="250808" sheetId="15" r:id="rId11"/>
+    <sheet name="250718" sheetId="14" r:id="rId12"/>
+    <sheet name="250704" sheetId="13" r:id="rId13"/>
+    <sheet name="250627" sheetId="12" r:id="rId14"/>
+    <sheet name="250620" sheetId="11" r:id="rId15"/>
+    <sheet name="250613" sheetId="10" r:id="rId16"/>
+    <sheet name="250530" sheetId="9" r:id="rId17"/>
+    <sheet name="250523" sheetId="8" r:id="rId18"/>
+    <sheet name="250516" sheetId="7" r:id="rId19"/>
+    <sheet name="250509" sheetId="6" r:id="rId20"/>
+    <sheet name="250502" sheetId="5" r:id="rId21"/>
+    <sheet name="250411" sheetId="4" r:id="rId22"/>
+    <sheet name="250221" sheetId="3" r:id="rId23"/>
+    <sheet name="250131" sheetId="2" r:id="rId24"/>
+    <sheet name="1230" sheetId="1" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="9">
   <si>
     <t>As end of</t>
   </si>
@@ -194,10 +195,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,6 +493,3592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBF739-2F19-494D-A086-1CD83BEB770E}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1528.26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>0.15286432009173076</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1226300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-823340</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.6714017777052923</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-633740</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.29843563106887555</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1080300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-592800</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.54873646209386284</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>4430140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2049880</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46271223934232325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6378700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1786510</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.28007430981234421</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>378420</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.9325567905686112E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10808840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3836390</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.35493077888099001</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46052</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1325.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1012060</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.57756091993380132</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1270445</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.3910866553794059</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-444820</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73726257168429077</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2727325</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.4866625387659837</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1619440</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.31343797781949795</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4346765</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40356787400054223</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45884</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>2.7798295567374047E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-211740</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70547078030252552</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1336730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.38144332838717043</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1054720</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.68322385893997695</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2603190</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4867340528169804</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5138100</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1748790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34035733053074091</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>299817.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.8351861583075461E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10486380</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4351980</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.41501261636522802</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5348280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2470830</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10377630</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4202620</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2470830</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10377630</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4202620</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45863</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1217.1500000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>416540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-284400</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68276756133864691</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1326800</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36942267266222106</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1152920</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.7063422045777582</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5640330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2764120</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.49006352465192637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1802045</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35781484239265327</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10676580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4566165</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.42768049319164003</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45856</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>7.7361287211814803E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>503540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-350840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.69674703102037572</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1314900</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36610933997856077</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1153940</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.70696711267950796</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5727330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2819680</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.49232015616351771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1834700</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.36429883345743358</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10763580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4654380</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.43241932516876358</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5901330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3097650</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10893580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5003995</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5901330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3097650</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10893580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5003995</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3389330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11078080</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5334700</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3389330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11078080</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5334700</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3437705</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11058430</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5421920</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3437705</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11058430</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5421920</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D16" s="5" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6286830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3430330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11258428</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5300498</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D4" s="5" t="e" cm="1">
+        <f t="array" ref="D4">B61632240=C4/B4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6286830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3430330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11258428</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5300498</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3439950</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5183728</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3439950</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5183728</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3447470</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5178568</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3447470</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5178568</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45793</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1195.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.2527458007828689E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-679870</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.36924773113625131</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1443820</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.60651963873135895</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1312520</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66382763503944975</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6198930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3436210</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55432308479043968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1727818</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34753775345472421</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11170528</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5164028</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46229041277189403</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45793</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1195.77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.2527458007828689E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-679870</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.36924773113625131</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1443820</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.60651963873135895</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1312520</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66382763503944975</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6198930</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3436210</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55432308479043968</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1727818</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34753775345472421</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11170528</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5164028</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46229041277189403</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45786</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1210.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>9.975145540376016E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-710950</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.38612775155738283</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1391200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.58441503885738288</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>2091200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1352900</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.64694912012241779</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6312930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3455050</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5472973722186053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4924600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1735475</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35240933273768427</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>265724.25</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.3958544856435038E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11237530</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5190525</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46189198160093897</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -821,2941 +4404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2470830</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10377630</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4202620</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45863</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1217.1500000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>416540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-284400</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.68276756133864691</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1326800</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36942267266222106</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1152920</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.7063422045777582</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5640330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2764120</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.49006352465192637</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1802045</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35781484239265327</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10676580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4566165</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.42768049319164003</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45856</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1206.58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>7.7361287211814803E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>503540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-350840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.69674703102037572</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1314900</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36610933997856077</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1153940</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.70696711267950796</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5727330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2819680</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.49232015616351771</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1834700</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.36429883345743358</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10763580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4654380</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.43241932516876358</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5901330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3097650</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10893580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5003995</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5901330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3097650</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10893580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5003995</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3389330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11078080</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5334700</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3389330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11078080</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5334700</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3437705</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11058430</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5421920</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3437705</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11058430</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5421920</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D16" s="5" t="e">
-        <v>#NAME?</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6286830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3430330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11258428</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5300498</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D4" s="5" t="e" cm="1">
-        <f t="array" ref="D4">B61632240=C4/B4</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6286830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3430330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11258428</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5300498</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3439950</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5183728</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3439950</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5183728</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3447470</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5178568</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3447470</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5178568</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45793</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1195.77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.2527458007828689E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-679870</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.36924773113625131</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1443820</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.60651963873135895</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1312520</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66382763503944975</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6198930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3436210</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55432308479043968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1727818</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34753775345472421</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11170528</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5164028</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46229041277189403</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45793</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1195.77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.2527458007828689E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-679870</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.36924773113625131</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1443820</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.60651963873135895</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1312520</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66382763503944975</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6198930</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3436210</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55432308479043968</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1727818</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34753775345472421</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11170528</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5164028</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46229041277189403</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45786</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1210.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>9.975145540376016E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-710950</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.38612775155738283</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1391200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.58441503885738288</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>2091200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1352900</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.64694912012241779</v>
-      </c>
-      <c r="E18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6312930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3455050</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5472973722186053</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4924600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1735475</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35240933273768427</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>265724.25</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.3958544856435038E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11237530</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5190525</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46189198160093897</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4081,333 +4730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>46386</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>2.3713087555403624E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-1063500</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.60691662386577638</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1303865</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.40137448052947516</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-447370</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74148904431995222</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5604140</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2814735</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.50225993640415834</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1652290</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.31979600131612052</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10770840</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4467025</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.41473320558099463</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45989</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1256.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-4.032836960672008E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1075520</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.61377617987787481</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1365410</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42032014776050486</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-449480</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74498624324593099</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5604140</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2890410</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.51576334638320953</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1747535</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.33823039851355796</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10770840</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4637945</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.43060197719026555</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBF241-CA72-4CB5-8C3F-136F3E8408B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4733,7 +5056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D4DEBF-7012-4D3C-9A89-43C32C47B6EC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5059,7 +5382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4D270-1B52-4C5B-9E28-60314EA92662}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5385,7 +5708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4C31B2-332E-43CB-8F48-59EA1BD2A5D3}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5711,7 +6034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6041,6 +6364,332 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46386</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>2.3713087555403624E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-1063500</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.60691662386577638</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1303865</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.40137448052947516</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-447370</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74148904431995222</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5604140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2814735</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.50225993640415834</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1652290</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.31979600131612052</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10770840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4467025</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.41473320558099463</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45989</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1256.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-4.032836960672008E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1075520</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.61377617987787481</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1365410</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42032014776050486</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-449480</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74498624324593099</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2890410</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.51576334638320953</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1747535</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.33823039851355796</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4637945</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.43060197719026555</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6366,7 +7015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FC00D-7E5D-4548-BEF2-5CBFB9DBC724}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6692,7 +7341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7018,7 +7667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7344,7 +7993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7670,7 +8319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7994,330 +8643,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45884</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>2.7798295567374047E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-211740</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70547078030252552</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1336730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.38144332838717043</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1054720</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.68322385893997695</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2603190</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.4867340528169804</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5138100</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1748790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34035733053074091</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>299817.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.8351861583075461E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10486380</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4351980</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.41501261636522802</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5348280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2470830</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10377630</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4202620</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -1,43 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBED09B0-0CE9-4646-8AED-F3F94F4AF963}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEA166C-CB4C-4A2D-BB86-03E177E790FF}"/>
   <bookViews>
-    <workbookView xWindow="14412" yWindow="828" windowWidth="8844" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14412" yWindow="1356" windowWidth="8676" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="260227" sheetId="25" r:id="rId1"/>
-    <sheet name="260130" sheetId="24" r:id="rId2"/>
-    <sheet name="251230" sheetId="23" r:id="rId3"/>
-    <sheet name="251128" sheetId="22" r:id="rId4"/>
-    <sheet name="251031" sheetId="21" r:id="rId5"/>
-    <sheet name="250926" sheetId="20" r:id="rId6"/>
-    <sheet name="250919" sheetId="19" r:id="rId7"/>
-    <sheet name="250912" sheetId="18" r:id="rId8"/>
-    <sheet name="250905" sheetId="17" r:id="rId9"/>
-    <sheet name="250815" sheetId="16" r:id="rId10"/>
-    <sheet name="250808" sheetId="15" r:id="rId11"/>
-    <sheet name="250718" sheetId="14" r:id="rId12"/>
-    <sheet name="250704" sheetId="13" r:id="rId13"/>
-    <sheet name="250627" sheetId="12" r:id="rId14"/>
-    <sheet name="250620" sheetId="11" r:id="rId15"/>
-    <sheet name="250613" sheetId="10" r:id="rId16"/>
-    <sheet name="250530" sheetId="9" r:id="rId17"/>
-    <sheet name="250523" sheetId="8" r:id="rId18"/>
-    <sheet name="250516" sheetId="7" r:id="rId19"/>
-    <sheet name="250509" sheetId="6" r:id="rId20"/>
-    <sheet name="250502" sheetId="5" r:id="rId21"/>
-    <sheet name="250411" sheetId="4" r:id="rId22"/>
-    <sheet name="250221" sheetId="3" r:id="rId23"/>
-    <sheet name="250131" sheetId="2" r:id="rId24"/>
-    <sheet name="1230" sheetId="1" r:id="rId25"/>
+    <sheet name="260327" sheetId="26" r:id="rId1"/>
+    <sheet name="260227" sheetId="25" r:id="rId2"/>
+    <sheet name="260130" sheetId="24" r:id="rId3"/>
+    <sheet name="251230" sheetId="23" r:id="rId4"/>
+    <sheet name="251128" sheetId="22" r:id="rId5"/>
+    <sheet name="251031" sheetId="21" r:id="rId6"/>
+    <sheet name="250926" sheetId="20" r:id="rId7"/>
+    <sheet name="250919" sheetId="19" r:id="rId8"/>
+    <sheet name="250912" sheetId="18" r:id="rId9"/>
+    <sheet name="250905" sheetId="17" r:id="rId10"/>
+    <sheet name="250815" sheetId="16" r:id="rId11"/>
+    <sheet name="250808" sheetId="15" r:id="rId12"/>
+    <sheet name="250718" sheetId="14" r:id="rId13"/>
+    <sheet name="250704" sheetId="13" r:id="rId14"/>
+    <sheet name="250627" sheetId="12" r:id="rId15"/>
+    <sheet name="250620" sheetId="11" r:id="rId16"/>
+    <sheet name="250613" sheetId="10" r:id="rId17"/>
+    <sheet name="250530" sheetId="9" r:id="rId18"/>
+    <sheet name="250523" sheetId="8" r:id="rId19"/>
+    <sheet name="250516" sheetId="7" r:id="rId20"/>
+    <sheet name="250509" sheetId="6" r:id="rId21"/>
+    <sheet name="250502" sheetId="5" r:id="rId22"/>
+    <sheet name="250411" sheetId="4" r:id="rId23"/>
+    <sheet name="250221" sheetId="3" r:id="rId24"/>
+    <sheet name="250131" sheetId="2" r:id="rId25"/>
+    <sheet name="1230" sheetId="1" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="9">
   <si>
     <t>As end of</t>
   </si>
@@ -195,6 +196,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -493,6 +498,3592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AF01D4-BE50-4242-955E-6394FC68ECAB}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1447.05</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-5.3138863805896927E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-688800</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.68749376185248023</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-646515</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.30445152905054768</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-433140</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.51730562522393408</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>3962740</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-1768455</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.44627076214942185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6231700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1931040</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.30987371022353449</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>366227</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.876839385721392E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10194440</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3699495</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.36289340071646897</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1528.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0.15286432009173076</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1226300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-823340</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.6714017777052923</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-633740</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.29843563106887555</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1080300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-592800</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.54873646209386284</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>4430140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2049880</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.46271223934232325</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6378700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1786510</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.28007430981234421</v>
+      </c>
+      <c r="E21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>378420</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.9325567905686112E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10808840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3836390</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.35493077888099001</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45905</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1264.8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>4.2718076574930373E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>420640</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-211280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.50228223659186</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3588400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1320030</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36786032772266192</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-984800</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.63793125785430194</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5552780</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2516110</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.45312618184044751</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5128200</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1791305</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34930482430482429</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>295995.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.7719219219219221E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10680980</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4307415</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40327900623351043</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45884</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>2.7798295567374047E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-211740</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.70547078030252552</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1336730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.38144332838717043</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1054720</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.68322385893997695</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5348280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2603190</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.4867340528169804</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5138100</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1748790</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34035733053074091</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>299817.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.8351861583075461E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10486380</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4351980</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.41501261636522802</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45884</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>2.7798295567374047E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-211740</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70547078030252552</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1336730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.38144332838717043</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1054720</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.68322385893997695</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2603190</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4867340528169804</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5138100</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1748790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34035733053074091</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>299817.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.8351861583075461E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10486380</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4351980</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.41501261636522802</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5348280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2470830</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10377630</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4202620</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2470830</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10377630</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4202620</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45863</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1217.1500000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>416540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-284400</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68276756133864691</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1326800</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36942267266222106</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1152920</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.7063422045777582</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5640330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2764120</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.49006352465192637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1802045</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35781484239265327</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10676580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4566165</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.42768049319164003</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45856</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>7.7361287211814803E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>503540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-350840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.69674703102037572</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1314900</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36610933997856077</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1153940</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.70696711267950796</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5727330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2819680</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.49232015616351771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1834700</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.36429883345743358</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10763580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4654380</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.43241932516876358</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5901330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3097650</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10893580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5003995</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5901330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3097650</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10893580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5003995</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3389330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11078080</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5334700</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3389330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11078080</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5334700</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3437705</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11058430</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5421920</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3437705</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11058430</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5421920</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D16" s="5" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6286830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3430330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11258428</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5300498</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D4" s="5" t="e" cm="1">
+        <f t="array" ref="D4">B61632240=C4/B4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6286830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3430330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11258428</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5300498</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3439950</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5183728</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3439950</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5183728</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3447470</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5178568</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3447470</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5178568</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45793</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1195.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.2527458007828689E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-679870</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.36924773113625131</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2380500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1443820</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.60651963873135895</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1312520</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66382763503944975</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6198930</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3436210</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55432308479043968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1727818</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34753775345472421</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11170528</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5164028</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46229041277189403</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBF739-2F19-494D-A086-1CD83BEB770E}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -818,2941 +4409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45884</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>2.7798295567374047E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-211740</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70547078030252552</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1336730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.38144332838717043</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1054720</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.68322385893997695</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2603190</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.4867340528169804</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5138100</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1748790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34035733053074091</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>299817.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.8351861583075461E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10486380</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4351980</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.41501261636522802</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5348280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2470830</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10377630</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4202620</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2470830</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10377630</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4202620</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45863</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1217.1500000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>416540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-284400</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.68276756133864691</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1326800</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36942267266222106</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1152920</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.7063422045777582</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5640330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2764120</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.49006352465192637</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1802045</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35781484239265327</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10676580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4566165</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.42768049319164003</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45856</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1206.58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>7.7361287211814803E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>503540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-350840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.69674703102037572</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1314900</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36610933997856077</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1153940</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.70696711267950796</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5727330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2819680</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.49232015616351771</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1834700</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.36429883345743358</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10763580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4654380</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.43241932516876358</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5901330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3097650</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10893580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5003995</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5901330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3097650</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10893580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5003995</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3389330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11078080</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5334700</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3389330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11078080</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5334700</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3437705</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11058430</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5421920</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3437705</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11058430</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5421920</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D16" s="5" t="e">
-        <v>#NAME?</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6286830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3430330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11258428</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5300498</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D4" s="5" t="e" cm="1">
-        <f t="array" ref="D4">B61632240=C4/B4</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6286830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3430330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11258428</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5300498</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3439950</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5183728</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3439950</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5183728</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3447470</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5178568</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3447470</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5178568</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45793</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1195.77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.2527458007828689E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-679870</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.36924773113625131</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2380500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1443820</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.60651963873135895</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1312520</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66382763503944975</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6198930</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3436210</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55432308479043968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1727818</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34753775345472421</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11170528</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5164028</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46229041277189403</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4078,333 +4735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>46052</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1325.62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>5.2354981860328352E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-1012060</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.57756091993380132</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1270445</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.3910866553794059</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-444820</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73726257168429077</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5604140</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2727325</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.4866625387659837</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1619440</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.31343797781949795</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10770840</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4346765</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40356787400054223</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>46386</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>2.3713087555403624E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1063500</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.60691662386577638</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1303865</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.40137448052947516</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-447370</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74148904431995222</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5604140</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2814735</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.50225993640415834</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1652290</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.31979600131612052</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10770840</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4467025</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.41473320558099463</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4730,7 +5061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBF241-CA72-4CB5-8C3F-136F3E8408B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5056,7 +5387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D4DEBF-7012-4D3C-9A89-43C32C47B6EC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5382,7 +5713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4D270-1B52-4C5B-9E28-60314EA92662}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5708,7 +6039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4C31B2-332E-43CB-8F48-59EA1BD2A5D3}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6034,7 +6365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6364,6 +6695,332 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46052</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1325.62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>5.2354981860328352E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-1012060</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.57756091993380132</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1270445</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.3910866553794059</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-444820</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73726257168429077</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5604140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2727325</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4866625387659837</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1619440</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.31343797781949795</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10770840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4346765</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40356787400054223</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46386</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>2.3713087555403624E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1063500</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.60691662386577638</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1303865</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.40137448052947516</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-447370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74148904431995222</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2814735</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.50225993640415834</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1652290</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.31979600131612052</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4467025</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.41473320558099463</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6689,7 +7346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7015,7 +7672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FC00D-7E5D-4548-BEF2-5CBFB9DBC724}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7341,7 +7998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7667,7 +8324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7993,7 +8650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8317,330 +8974,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45905</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1264.8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>4.2718076574930373E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>420640</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-211280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.50228223659186</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3588400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1320030</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36786032772266192</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-984800</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.63793125785430194</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5552780</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2516110</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.45312618184044751</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5128200</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1791305</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34930482430482429</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>295995.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.7719219219219221E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10680980</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4307415</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40327900623351043</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45884</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>2.7798295567374047E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-211740</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.70547078030252552</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1336730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.38144332838717043</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1054720</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.68322385893997695</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5348280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2603190</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.4867340528169804</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5138100</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1748790</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34035733053074091</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>299817.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.8351861583075461E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10486380</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4351980</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.41501261636522802</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -1,44 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEA166C-CB4C-4A2D-BB86-03E177E790FF}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{688DDDF8-2187-40A8-96B0-9FBC146CE40C}"/>
   <bookViews>
-    <workbookView xWindow="14412" yWindow="1356" windowWidth="8676" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14028" yWindow="1104" windowWidth="9192" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="260327" sheetId="26" r:id="rId1"/>
-    <sheet name="260227" sheetId="25" r:id="rId2"/>
-    <sheet name="260130" sheetId="24" r:id="rId3"/>
-    <sheet name="251230" sheetId="23" r:id="rId4"/>
-    <sheet name="251128" sheetId="22" r:id="rId5"/>
-    <sheet name="251031" sheetId="21" r:id="rId6"/>
-    <sheet name="250926" sheetId="20" r:id="rId7"/>
-    <sheet name="250919" sheetId="19" r:id="rId8"/>
-    <sheet name="250912" sheetId="18" r:id="rId9"/>
-    <sheet name="250905" sheetId="17" r:id="rId10"/>
-    <sheet name="250815" sheetId="16" r:id="rId11"/>
-    <sheet name="250808" sheetId="15" r:id="rId12"/>
-    <sheet name="250718" sheetId="14" r:id="rId13"/>
-    <sheet name="250704" sheetId="13" r:id="rId14"/>
-    <sheet name="250627" sheetId="12" r:id="rId15"/>
-    <sheet name="250620" sheetId="11" r:id="rId16"/>
-    <sheet name="250613" sheetId="10" r:id="rId17"/>
-    <sheet name="250530" sheetId="9" r:id="rId18"/>
-    <sheet name="250523" sheetId="8" r:id="rId19"/>
-    <sheet name="250516" sheetId="7" r:id="rId20"/>
-    <sheet name="250509" sheetId="6" r:id="rId21"/>
-    <sheet name="250502" sheetId="5" r:id="rId22"/>
-    <sheet name="250411" sheetId="4" r:id="rId23"/>
-    <sheet name="250221" sheetId="3" r:id="rId24"/>
-    <sheet name="250131" sheetId="2" r:id="rId25"/>
-    <sheet name="1230" sheetId="1" r:id="rId26"/>
+    <sheet name="260430" sheetId="27" r:id="rId1"/>
+    <sheet name="260327" sheetId="26" r:id="rId2"/>
+    <sheet name="260227" sheetId="25" r:id="rId3"/>
+    <sheet name="260130" sheetId="24" r:id="rId4"/>
+    <sheet name="251230" sheetId="23" r:id="rId5"/>
+    <sheet name="251128" sheetId="22" r:id="rId6"/>
+    <sheet name="251031" sheetId="21" r:id="rId7"/>
+    <sheet name="250926" sheetId="20" r:id="rId8"/>
+    <sheet name="250919" sheetId="19" r:id="rId9"/>
+    <sheet name="250912" sheetId="18" r:id="rId10"/>
+    <sheet name="250905" sheetId="17" r:id="rId11"/>
+    <sheet name="250815" sheetId="16" r:id="rId12"/>
+    <sheet name="250808" sheetId="15" r:id="rId13"/>
+    <sheet name="250718" sheetId="14" r:id="rId14"/>
+    <sheet name="250704" sheetId="13" r:id="rId15"/>
+    <sheet name="250627" sheetId="12" r:id="rId16"/>
+    <sheet name="250620" sheetId="11" r:id="rId17"/>
+    <sheet name="250613" sheetId="10" r:id="rId18"/>
+    <sheet name="250530" sheetId="9" r:id="rId19"/>
+    <sheet name="250523" sheetId="8" r:id="rId20"/>
+    <sheet name="250516" sheetId="7" r:id="rId21"/>
+    <sheet name="250509" sheetId="6" r:id="rId22"/>
+    <sheet name="250502" sheetId="5" r:id="rId23"/>
+    <sheet name="250411" sheetId="4" r:id="rId24"/>
+    <sheet name="250221" sheetId="3" r:id="rId25"/>
+    <sheet name="250131" sheetId="2" r:id="rId26"/>
+    <sheet name="1230" sheetId="1" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="9">
   <si>
     <t>As end of</t>
   </si>
@@ -196,10 +197,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,6 +495,3592 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C9EE1D-23EE-4AB1-A659-146B57BE95C3}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46142</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1493.69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.2231090839984863E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-657400</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.65615330871344446</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2227540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-693215</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.31120204350988084</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-389600</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.46530514749790997</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>4066740</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-1740215</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4279140048294211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6271300</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1848915</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.29482164782421505</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>370977</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.9154720711814136E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10338040</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3589130</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.34717702775381021</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46108</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1447.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-5.3138863805896927E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-688800</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68749376185248023</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-646515</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.30445152905054768</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-433140</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.51730562522393408</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>3962740</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1768455</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.44627076214942185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6231700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1931040</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.30987371022353449</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>366227</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.876839385721392E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10194440</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3699495</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.36289340071646897</v>
+      </c>
+      <c r="E23">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45912</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1293.6199999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>2.2786211258696978E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-200500</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.66802158992470184</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3588400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1226640</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.34183480102552671</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-952600</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.61707282314379364</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5432280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2379740</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.43807388426222504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5128200</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1671190</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.3258823758823759</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>295995.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.7719219219219221E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10560480</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4050930</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.38359335939275485</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45905</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1264.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>4.2718076574930373E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>420640</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-211280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.50228223659186</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3588400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1320030</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36786032772266192</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-984800</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.63793125785430194</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5552780</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2516110</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.45312618184044751</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5128200</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1791305</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34930482430482429</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>295995.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.7719219219219221E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10680980</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4307415</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40327900623351043</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45905</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1264.8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>4.2718076574930373E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>420640</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-211280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.50228223659186</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3588400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1320030</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36786032772266192</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-984800</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.63793125785430194</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5552780</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2516110</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.45312618184044751</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5128200</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1791305</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34930482430482429</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>295995.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.7719219219219221E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10680980</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4307415</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40327900623351043</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45884</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>2.7798295567374047E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-211740</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.70547078030252552</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1336730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.38144332838717043</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1054720</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.68322385893997695</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5348280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2603190</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.4867340528169804</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5138100</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1748790</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34035733053074091</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>299817.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.8351861583075461E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10486380</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4351980</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.41501261636522802</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45884</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>2.7798295567374047E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-211740</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70547078030252552</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1336730</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.38144332838717043</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1054720</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.68322385893997695</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2603190</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4867340528169804</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5138100</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1748790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34035733053074091</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>299817.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.8351861583075461E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10486380</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4351980</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.41501261636522802</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5348280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2470830</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10377630</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4202620</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45877</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1259.07</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.444111243478605E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-210840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.70247217964949693</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3504400</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1225490</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.34970037666932996</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1034500</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.67012579838573849</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5348280</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2470830</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46198590948865803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5029350</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1731790</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.34433674331673081</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.5011084931452375E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10377630</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4202620</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.40496914998896666</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45863</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1217.1500000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>416540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-284400</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68276756133864691</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1326800</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36942267266222106</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1152920</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.7063422045777582</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5640330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2764120</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.49006352465192637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1802045</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35781484239265327</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10676580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4566165</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.42768049319164003</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45856</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1206.58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>7.7361287211814803E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>503540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-350840</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.69674703102037572</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1314900</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36610933997856077</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1153940</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.70696711267950796</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5727330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2819680</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.49232015616351771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5036250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1834700</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.36429883345743358</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>276670</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4935716058575328E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10763580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4654380</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.43241932516876358</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5901330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3097650</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10893580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5003995</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45842</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1119.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.4663069788067456E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>677540</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-489280</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.72214186616288334</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1415000</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39398031490582058</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1193370</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73112409939714751</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5901330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3097650</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.5249070972136789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1906345</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.3818608843707747</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10893580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5003995</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.45935266459694607</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3389330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11078080</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5334700</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45835</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1082.42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>1.3853113906503154E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-638120</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.740244072200826</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1535300</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42747560245576421</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1215910</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.74493334313581339</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3389330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55692157027061218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4992250</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1945370</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.38967800090139715</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>273102</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4705193049226303E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11078080</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5334700</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.48155456541205699</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6085830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3437705</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11058430</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5421920</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45828</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1067.6300000000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-4.9051393960986851E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>862040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-661565</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.76744118602385036</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1538750</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.42843619050270776</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1237390</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.75809317257266084</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6085830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3437705</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.56487036279357128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4972600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1984215</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.39902968266098221</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4559536258697666E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11058430</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5421920</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.49029744728682101</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D16" s="5" t="e">
+        <v>#NAME?</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6286830</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3430330</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11258428</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5300498</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45821</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1122.7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3042517273186111E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1063040</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-805890</v>
+      </c>
+      <c r="D4" s="5" t="e" cm="1">
+        <f t="array" ref="D4">B61632240=C4/B4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3591550</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1423200</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.39626345171304866</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1632240</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1201240</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.73594569426064793</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6286830</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3430330</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.54563746753133135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1870168</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.37617039833067756</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11258428</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5300498</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.47080267333947512</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3439950</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5183728</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45807</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1149.18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-2.3105171886157162E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-683180</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.37104544244879784</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1440450</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.59772189717415658</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-1316320</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.66574954481084359</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>6228330</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-3439950</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.55230695868716018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1743778</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.35074798887601127</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>11199928</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-5183728</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.46283583251606619</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45800</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1176.3599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-1.6232218570460942E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1841230</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-662540</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.35983554471738999</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2409900</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1468730</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.6094568239346031</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1977200</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1316200</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.66568885292332591</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>6228330</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3447470</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55351434493676477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>4971598</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1731098</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.34819750108516417</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>271302.75</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4570532452543424E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>11199928</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5178568</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.46237511526859815</v>
+      </c>
+      <c r="E23">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AF01D4-BE50-4242-955E-6394FC68ECAB}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -823,2941 +4406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45905</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1264.8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>4.2718076574930373E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>420640</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-211280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.50228223659186</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3588400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1320030</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36786032772266192</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-984800</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.63793125785430194</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5552780</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2516110</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.45312618184044751</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5128200</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1791305</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34930482430482429</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>295995.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.7719219219219221E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10680980</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4307415</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40327900623351043</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45884</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>2.7798295567374047E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-211740</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.70547078030252552</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1336730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.38144332838717043</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1054720</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.68322385893997695</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5348280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2603190</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.4867340528169804</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5138100</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1748790</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34035733053074091</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>299817.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.8351861583075461E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10486380</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4351980</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.41501261636522802</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45884</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>2.7798295567374047E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-211740</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70547078030252552</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1336730</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.38144332838717043</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1054720</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.68322385893997695</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2603190</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.4867340528169804</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5138100</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1748790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34035733053074091</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>299817.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.8351861583075461E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10486380</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4351980</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.41501261636522802</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5348280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2470830</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10377630</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4202620</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45877</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1259.07</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.444111243478605E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-210840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.70247217964949693</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3504400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1225490</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.34970037666932996</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1034500</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.67012579838573849</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5348280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2470830</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.46198590948865803</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5029350</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1731790</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.34433674331673081</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.5011084931452375E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10377630</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4202620</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.40496914998896666</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45863</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1217.1500000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>416540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-284400</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.68276756133864691</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1326800</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36942267266222106</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1152920</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.7063422045777582</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5640330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2764120</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.49006352465192637</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1802045</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35781484239265327</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10676580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4566165</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.42768049319164003</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45856</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1206.58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>7.7361287211814803E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>503540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-350840</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.69674703102037572</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1314900</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36610933997856077</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1153940</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.70696711267950796</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5727330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2819680</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.49232015616351771</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5036250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1834700</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.36429883345743358</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>276670</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4935716058575328E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10763580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4654380</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.43241932516876358</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5901330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3097650</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10893580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5003995</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45842</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1119.94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>3.4663069788067456E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>677540</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-489280</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.72214186616288334</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1415000</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39398031490582058</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1193370</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73112409939714751</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5901330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3097650</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.5249070972136789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1906345</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.3818608843707747</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10893580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5003995</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.45935266459694607</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3389330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11078080</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5334700</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45835</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1082.42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>1.3853113906503154E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-638120</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.740244072200826</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1535300</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42747560245576421</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1215910</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.74493334313581339</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3389330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55692157027061218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4992250</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1945370</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.38967800090139715</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>273102</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4705193049226303E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11078080</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5334700</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.48155456541205699</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6085830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3437705</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11058430</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5421920</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45828</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1067.6300000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-4.9051393960986851E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>862040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-661565</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.76744118602385036</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1538750</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.42843619050270776</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1237390</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.75809317257266084</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6085830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3437705</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.56487036279357128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4972600</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1984215</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.39902968266098221</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4559536258697666E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11058430</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5421920</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.49029744728682101</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D16" s="5" t="e">
-        <v>#NAME?</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6286830</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3430330</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11258428</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5300498</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45821</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1122.7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3042517273186111E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1063040</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-805890</v>
-      </c>
-      <c r="D4" s="5" t="e" cm="1">
-        <f t="array" ref="D4">B61632240=C4/B4</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3591550</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1423200</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.39626345171304866</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1632240</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1201240</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.73594569426064793</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6286830</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3430330</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.54563746753133135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1870168</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.37617039833067756</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11258428</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5300498</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.47080267333947512</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3439950</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5183728</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45807</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1149.18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-2.3105171886157162E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-683180</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.37104544244879784</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1440450</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.59772189717415658</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-1316320</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.66574954481084359</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>6228330</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-3439950</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.55230695868716018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1743778</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.35074798887601127</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>11199928</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-5183728</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.46283583251606619</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45800</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1176.3599999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-1.6232218570460942E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1841230</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-662540</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.35983554471738999</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2409900</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1468730</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.6094568239346031</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1977200</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1316200</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.66568885292332591</v>
-      </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>6228330</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3447470</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.55351434493676477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4971598</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1731098</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34819750108516417</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>271302.75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4570532452543424E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>11199928</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5178568</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.46237511526859815</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4083,333 +4732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBF739-2F19-494D-A086-1CD83BEB770E}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>46080</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1528.26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>0.15286432009173076</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1226300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-823340</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.6714017777052923</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2123540</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-633740</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.29843563106887555</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1080300</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-592800</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.54873646209386284</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>4430140</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2049880</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.46271223934232325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>6378700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1786510</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.28007430981234421</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>378420</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.9325567905686112E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10808840</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-3836390</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.35493077888099001</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>46052</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1325.62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1012060</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.57756091993380132</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3248500</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1270445</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.3910866553794059</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>603340</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-444820</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.73726257168429077</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5604140</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2727325</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.4866625387659837</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1619440</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.31343797781949795</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>284160</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.4998354849323555E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10770840</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4346765</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40356787400054223</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4735,7 +5058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5061,7 +5384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBF241-CA72-4CB5-8C3F-136F3E8408B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5387,7 +5710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D4DEBF-7012-4D3C-9A89-43C32C47B6EC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5713,7 +6036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4D270-1B52-4C5B-9E28-60314EA92662}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6039,7 +6362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4C31B2-332E-43CB-8F48-59EA1BD2A5D3}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6365,7 +6688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6695,6 +7018,332 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBF739-2F19-494D-A086-1CD83BEB770E}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1528.26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>0.15286432009173076</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1226300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-823340</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.6714017777052923</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-633740</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.29843563106887555</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1080300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-592800</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.54873646209386284</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>4430140</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2049880</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.46271223934232325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6378700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1786510</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.28007430981234421</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>378420</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.9325567905686112E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10808840</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3836390</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.35493077888099001</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46052</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1325.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1012060</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.57756091993380132</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3248500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1270445</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.3910866553794059</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>603340</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-444820</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.73726257168429077</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5604140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2727325</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.4866625387659837</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1619440</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.31343797781949795</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>284160</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.4998354849323555E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10770840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4346765</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.40356787400054223</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7020,7 +7669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7346,7 +7995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7672,7 +8321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FC00D-7E5D-4548-BEF2-5CBFB9DBC724}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7998,7 +8647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8324,7 +8973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8648,330 +9297,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45912</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1293.6199999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>2.2786211258696978E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-200500</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.66802158992470184</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3588400</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1226640</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.34183480102552671</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-952600</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.61707282314379364</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5432280</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2379740</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.43807388426222504</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5128200</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1671190</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.3258823758823759</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>295995.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.7719219219219221E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10560480</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4050930</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.38359335939275485</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45905</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1264.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>4.2718076574930373E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>420640</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-211280</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.50228223659186</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3588400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1320030</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36786032772266192</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-984800</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.63793125785430194</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5552780</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2516110</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.45312618184044751</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5128200</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1791305</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.34930482430482429</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>295995.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.7719219219219221E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10680980</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4307415</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.40327900623351043</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Excel/04-Amt-by-period.xlsx
+++ b/Excel/04-Amt-by-period.xlsx
@@ -1,45 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="355" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{688DDDF8-2187-40A8-96B0-9FBC146CE40C}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="11_4407D90E547F242EEA22E4B75BC69E7FC8C566A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA562E8C-CA57-4B63-975C-AA7DED9CBD15}"/>
   <bookViews>
-    <workbookView xWindow="14028" yWindow="1104" windowWidth="9192" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13548" yWindow="1044" windowWidth="9468" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="260430" sheetId="27" r:id="rId1"/>
-    <sheet name="260327" sheetId="26" r:id="rId2"/>
-    <sheet name="260227" sheetId="25" r:id="rId3"/>
-    <sheet name="260130" sheetId="24" r:id="rId4"/>
-    <sheet name="251230" sheetId="23" r:id="rId5"/>
-    <sheet name="251128" sheetId="22" r:id="rId6"/>
-    <sheet name="251031" sheetId="21" r:id="rId7"/>
-    <sheet name="250926" sheetId="20" r:id="rId8"/>
-    <sheet name="250919" sheetId="19" r:id="rId9"/>
-    <sheet name="250912" sheetId="18" r:id="rId10"/>
-    <sheet name="250905" sheetId="17" r:id="rId11"/>
-    <sheet name="250815" sheetId="16" r:id="rId12"/>
-    <sheet name="250808" sheetId="15" r:id="rId13"/>
-    <sheet name="250718" sheetId="14" r:id="rId14"/>
-    <sheet name="250704" sheetId="13" r:id="rId15"/>
-    <sheet name="250627" sheetId="12" r:id="rId16"/>
-    <sheet name="250620" sheetId="11" r:id="rId17"/>
-    <sheet name="250613" sheetId="10" r:id="rId18"/>
-    <sheet name="250530" sheetId="9" r:id="rId19"/>
-    <sheet name="250523" sheetId="8" r:id="rId20"/>
-    <sheet name="250516" sheetId="7" r:id="rId21"/>
-    <sheet name="250509" sheetId="6" r:id="rId22"/>
-    <sheet name="250502" sheetId="5" r:id="rId23"/>
-    <sheet name="250411" sheetId="4" r:id="rId24"/>
-    <sheet name="250221" sheetId="3" r:id="rId25"/>
-    <sheet name="250131" sheetId="2" r:id="rId26"/>
-    <sheet name="1230" sheetId="1" r:id="rId27"/>
+    <sheet name="260630" sheetId="29" r:id="rId1"/>
+    <sheet name="260529" sheetId="28" r:id="rId2"/>
+    <sheet name="260430" sheetId="27" r:id="rId3"/>
+    <sheet name="260327" sheetId="26" r:id="rId4"/>
+    <sheet name="260227" sheetId="25" r:id="rId5"/>
+    <sheet name="260130" sheetId="24" r:id="rId6"/>
+    <sheet name="251230" sheetId="23" r:id="rId7"/>
+    <sheet name="251128" sheetId="22" r:id="rId8"/>
+    <sheet name="251031" sheetId="21" r:id="rId9"/>
+    <sheet name="250926" sheetId="20" r:id="rId10"/>
+    <sheet name="250919" sheetId="19" r:id="rId11"/>
+    <sheet name="250912" sheetId="18" r:id="rId12"/>
+    <sheet name="250905" sheetId="17" r:id="rId13"/>
+    <sheet name="250815" sheetId="16" r:id="rId14"/>
+    <sheet name="250808" sheetId="15" r:id="rId15"/>
+    <sheet name="250718" sheetId="14" r:id="rId16"/>
+    <sheet name="250704" sheetId="13" r:id="rId17"/>
+    <sheet name="250627" sheetId="12" r:id="rId18"/>
+    <sheet name="250620" sheetId="11" r:id="rId19"/>
+    <sheet name="250613" sheetId="10" r:id="rId20"/>
+    <sheet name="250530" sheetId="9" r:id="rId21"/>
+    <sheet name="250523" sheetId="8" r:id="rId22"/>
+    <sheet name="250516" sheetId="7" r:id="rId23"/>
+    <sheet name="250509" sheetId="6" r:id="rId24"/>
+    <sheet name="250502" sheetId="5" r:id="rId25"/>
+    <sheet name="250411" sheetId="4" r:id="rId26"/>
+    <sheet name="250221" sheetId="3" r:id="rId27"/>
+    <sheet name="250131" sheetId="2" r:id="rId28"/>
+    <sheet name="1230" sheetId="1" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="9">
   <si>
     <t>As end of</t>
   </si>
@@ -197,6 +199,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -495,7 +501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C9EE1D-23EE-4AB1-A659-146B57BE95C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBB6983-FE58-4211-BE24-E136A3ACD317}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -509,19 +515,19 @@
         <v>0</v>
       </c>
       <c r="C1" s="9">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1">
-        <v>1493.69</v>
+        <v>1568.37</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E2" s="8">
         <f>(E1-E13)/E13</f>
-        <v>3.2231090839984863E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -549,11 +555,11 @@
         <v>1001900</v>
       </c>
       <c r="C4" s="7">
-        <v>-657400</v>
+        <v>-676300</v>
       </c>
       <c r="D4" s="5">
         <f>C4/B4</f>
-        <v>-0.65615330871344446</v>
+        <v>-0.67501746681305519</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -567,11 +573,11 @@
         <v>2227540</v>
       </c>
       <c r="C5" s="7">
-        <v>-693215</v>
+        <v>-648625</v>
       </c>
       <c r="D5" s="5">
         <f>C5/B5</f>
-        <v>-0.31120204350988084</v>
+        <v>-0.29118444562162743</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -585,11 +591,11 @@
         <v>837300</v>
       </c>
       <c r="C6" s="7">
-        <v>-389600</v>
+        <v>-409100</v>
       </c>
       <c r="D6" s="5">
         <f>C6/B6</f>
-        <v>-0.46530514749790997</v>
+        <v>-0.48859429117401171</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -603,11 +609,11 @@
       </c>
       <c r="C7" s="6">
         <f>SUM(C4:C6)</f>
-        <v>-1740215</v>
+        <v>-1734025</v>
       </c>
       <c r="D7" s="5">
         <f>C7/B7</f>
-        <v>-0.4279140048294211</v>
+        <v>-0.42639190112965175</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -622,27 +628,27 @@
         <v>2</v>
       </c>
       <c r="B9" s="7">
-        <v>6271300</v>
+        <v>6531800</v>
       </c>
       <c r="C9" s="7">
-        <v>-1848915</v>
+        <v>-1827330</v>
       </c>
       <c r="D9" s="5">
         <f>C9/B9</f>
-        <v>-0.29482164782421505</v>
+        <v>-0.27975902507731404</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="C10" s="7">
-        <v>370977</v>
+        <v>389724</v>
       </c>
       <c r="D10" s="5">
         <f>C10/B9</f>
-        <v>5.9154720711814136E-2</v>
+        <v>5.9665635812486607E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -651,19 +657,19 @@
       </c>
       <c r="B11" s="6">
         <f>B7+B9</f>
-        <v>10338040</v>
+        <v>10598540</v>
       </c>
       <c r="C11" s="6">
         <f>C7+C9</f>
-        <v>-3589130</v>
+        <v>-3561355</v>
       </c>
       <c r="D11" s="5">
         <f>C11/B11</f>
-        <v>-0.34717702775381021</v>
+        <v>-0.3360231692289693</v>
       </c>
       <c r="E11">
         <f>E4+E5+E6+E9</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -671,18 +677,18 @@
         <v>0</v>
       </c>
       <c r="C13" s="9">
-        <v>46108</v>
+        <v>46171</v>
       </c>
       <c r="D13" t="s">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1447.05</v>
+        <v>1568.37</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E14" s="8">
-        <v>-5.3138863805896927E-2</v>
+        <v>4.9996987326687489E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -710,10 +716,10 @@
         <v>1001900</v>
       </c>
       <c r="C16" s="7">
-        <v>-688800</v>
+        <v>-670940</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.68749376185248023</v>
+        <v>-0.66966763150014974</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -724,13 +730,13 @@
         <v>3</v>
       </c>
       <c r="B17" s="7">
-        <v>2123540</v>
+        <v>2227540</v>
       </c>
       <c r="C17" s="7">
-        <v>-646515</v>
+        <v>-673625</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.30445152905054768</v>
+        <v>-0.30240758864038358</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -744,10 +750,10 @@
         <v>837300</v>
       </c>
       <c r="C18" s="7">
-        <v>-433140</v>
+        <v>-401700</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.51730562522393408</v>
+        <v>-0.47975635972769615</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -756,13 +762,13 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="6">
-        <v>3962740</v>
+        <v>4066740</v>
       </c>
       <c r="C19" s="6">
-        <v>-1768455</v>
+        <v>-1746265</v>
       </c>
       <c r="D19" s="5">
-        <v>-0.44627076214942185</v>
+        <v>-0.42940168292047193</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,25 +783,25 @@
         <v>2</v>
       </c>
       <c r="B21" s="7">
-        <v>6231700</v>
+        <v>6343800</v>
       </c>
       <c r="C21" s="7">
-        <v>-1931040</v>
+        <v>-1952095</v>
       </c>
       <c r="D21" s="5">
-        <v>-0.30987371022353449</v>
+        <v>-0.30771698351145998</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="7">
-        <v>366227</v>
+        <v>375294</v>
       </c>
       <c r="D22" s="5">
-        <v>5.876839385721392E-2</v>
+        <v>5.9159179040953372E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -803,16 +809,16 @@
         <v>8</v>
       </c>
       <c r="B23" s="6">
-        <v>10194440</v>
+        <v>10410540</v>
       </c>
       <c r="C23" s="6">
-        <v>-3699495</v>
+        <v>-3698360</v>
       </c>
       <c r="D23" s="5">
-        <v>-0.36289340071646897</v>
+        <v>-0.35525150472501904</v>
       </c>
       <c r="E23">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -821,6 +827,658 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45926</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1278.74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-1.0814406832105961E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-890220</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.50802944701249786</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3249040</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1208130</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.37184214414103861</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>572540</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-401820</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.70181996017745485</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5573880</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2500170</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.44855109905487739</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1681725</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.32549306133508815</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>298535.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.7780730446900345E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10740580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4181895</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.38935467172163885</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45919</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1292.72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-6.9572208221878426E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-863680</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.49288363864635049</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3249040</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1195800</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.36804717701228673</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>572540</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-399520</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.6978027736053376</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5573880</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2459000</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.44116486181977366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1666195</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.32248727427564983</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>298535.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.7780730446900345E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10740580</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4125195</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.38407562720076571</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>45919</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1292.72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-6.9572208221878426E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1752300</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-863680</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.49288363864635049</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3249040</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-1195800</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.36804717701228673</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>572540</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-399520</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.6978027736053376</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>5573880</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-2459000</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.44116486181977366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5166700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1666195</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.32248727427564983</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>298535.7</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.7780730446900345E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10740580</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-4125195</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.38407562720076571</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45912</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1293.6199999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>300140</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-200500</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.66802158992470184</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3588400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1226640</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.34183480102552671</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1543740</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-952600</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.61707282314379364</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>5432280</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2379740</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.43807388426222504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5128200</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1671190</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.3258823758823759</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>295995.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.7719219219219221E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10560480</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4050930</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.38359335939275485</v>
+      </c>
+      <c r="E23">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699E09FF-5543-4627-B869-059368E93B21}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1146,7 +1804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376E0E9D-AFC7-48C4-8BA4-CDBEFA563129}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1472,7 +2130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F400C-8AD0-4837-BB77-C3C717B678B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1798,7 +2456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F32CB65-9456-4E75-B848-3BAB2F7365C7}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2124,7 +2782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9EF463-2F30-449E-9ACA-B3134C3C5447}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2450,7 +3108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA7DE61-BBCF-4D9C-9297-1085B1D8263C}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2776,7 +3434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373050F8-72D0-4C2F-8B80-26C88CE91628}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3102,7 +3760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E153650-B0E8-466D-8F31-78659B503768}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3428,7 +4086,333 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D71667-8E08-47C3-840C-3C930D895CE8}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1568.37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>4.9996987326687489E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-670940</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.66966763150014974</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2227540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-673625</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.30240758864038358</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-401700</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.47975635972769615</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>4066740</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-1746265</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.42940168292047193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6343800</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1952095</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.30771698351145998</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>375294</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.9159179040953372E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10410540</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3698360</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.35525150472501904</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46142</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1493.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>3.2231090839984863E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-657400</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.65615330871344446</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2227540</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-693215</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.31120204350988084</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-389600</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.46530514749790997</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>4066740</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1740215</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.4279140048294211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6271300</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1848915</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.29482164782421505</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>370977</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.9154720711814136E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10338040</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3589130</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.34717702775381021</v>
+      </c>
+      <c r="E23">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552CD9C1-2030-4328-9D69-E157E8DC4B84}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3754,7 +4738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC193AA-68B5-4D75-8672-E97855DF0173}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4080,333 +5064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AF01D4-BE50-4242-955E-6394FC68ECAB}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>46108</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1447.05</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-5.3138863805896927E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1001900</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-688800</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.68749376185248023</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>2123540</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-646515</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.30445152905054768</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>837300</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-433140</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.51730562522393408</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>3962740</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-1768455</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.44627076214942185</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>6231700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1931040</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.30987371022353449</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>366227</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.876839385721392E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10194440</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-3699495</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.36289340071646897</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>46080</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1528.26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0.15286432009173076</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1226300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-823340</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.6714017777052923</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2123540</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-633740</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.29843563106887555</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1080300</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-592800</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.54873646209386284</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>4430140</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2049880</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.46271223934232325</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>6378700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1786510</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.28007430981234421</v>
-      </c>
-      <c r="E21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>378420</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.9325567905686112E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10808840</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3836390</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.35493077888099001</v>
-      </c>
-      <c r="E23">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DD628C-CC42-43B0-A721-1E91130D13A5}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4732,7 +5390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D397C17-7D11-44D9-80F7-712E06707A25}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5058,7 +5716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4B6815-B29A-446B-B4C9-96F02B6A5E9D}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5384,7 +6042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEBF241-CA72-4CB5-8C3F-136F3E8408B6}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5710,7 +6368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D4DEBF-7012-4D3C-9A89-43C32C47B6EC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6036,7 +6694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4D270-1B52-4C5B-9E28-60314EA92662}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6362,7 +7020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4C31B2-332E-43CB-8F48-59EA1BD2A5D3}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6688,7 +7346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7018,6 +7676,658 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C9EE1D-23EE-4AB1-A659-146B57BE95C3}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46142</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1493.69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>3.2231090839984863E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-657400</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.65615330871344446</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2227540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-693215</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.31120204350988084</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-389600</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.46530514749790997</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>4066740</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-1740215</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.4279140048294211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6271300</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1848915</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.29482164782421505</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>370977</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.9154720711814136E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10338040</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3589130</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.34717702775381021</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46108</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1447.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>-5.3138863805896927E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-688800</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.68749376185248023</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-646515</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.30445152905054768</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-433140</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.51730562522393408</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>3962740</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1768455</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.44627076214942185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6231700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1931040</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.30987371022353449</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>366227</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.876839385721392E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10194440</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3699495</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.36289340071646897</v>
+      </c>
+      <c r="E23">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35AF01D4-BE50-4242-955E-6394FC68ECAB}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9">
+        <v>46108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>1447.05</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="8">
+        <f>(E1-E13)/E13</f>
+        <v>-5.3138863805896927E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1001900</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-688800</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4/B4</f>
+        <v>-0.68749376185248023</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-646515</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/B5</f>
+        <v>-0.30445152905054768</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>837300</v>
+      </c>
+      <c r="C6" s="7">
+        <v>-433140</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6/B6</f>
+        <v>-0.51730562522393408</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v>3962740</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v>-1768455</v>
+      </c>
+      <c r="D7" s="5">
+        <f>C7/B7</f>
+        <v>-0.44627076214942185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6231700</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1931040</v>
+      </c>
+      <c r="D9" s="5">
+        <f>C9/B9</f>
+        <v>-0.30987371022353449</v>
+      </c>
+      <c r="E9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
+        <v>366227</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10/B9</f>
+        <v>5.876839385721392E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B7+B9</f>
+        <v>10194440</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C7+C9</f>
+        <v>-3699495</v>
+      </c>
+      <c r="D11" s="5">
+        <f>C11/B11</f>
+        <v>-0.36289340071646897</v>
+      </c>
+      <c r="E11">
+        <f>E4+E5+E6+E9</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1528.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="8">
+        <v>0.15286432009173076</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>4</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1226300</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-823340</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.6714017777052923</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2123540</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-633740</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.29843563106887555</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1080300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-592800</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.54873646209386284</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6">
+        <v>4430140</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2049880</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.46271223934232325</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="6"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6378700</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1786510</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.28007430981234421</v>
+      </c>
+      <c r="E21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7">
+        <v>378420</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5.9325567905686112E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10808840</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3836390</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.35493077888099001</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0EBF739-2F19-494D-A086-1CD83BEB770E}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7343,7 +8653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571141AB-5414-4FC9-BC5C-CFDAE3DA04A4}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7669,7 +8979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66219EEC-5DA1-4A33-9F60-7AB6DE9863CC}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7995,7 +9305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C8022-6FAB-4827-AFA2-E1EDA7432C87}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8321,7 +9631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FC00D-7E5D-4548-BEF2-5CBFB9DBC724}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8645,656 +9955,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142E41C8-5056-4759-B54A-4980815EFEAB}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45926</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1278.74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-1.0814406832105961E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-890220</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.50802944701249786</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3249040</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1208130</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.37184214414103861</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>572540</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-401820</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.70181996017745485</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5573880</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2500170</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.44855109905487739</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1681725</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.32549306133508815</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>298535.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.7780730446900345E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10740580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4181895</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.38935467172163885</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45919</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1292.72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>-6.9572208221878426E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-863680</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.49288363864635049</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3249040</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1195800</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.36804717701228673</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>572540</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-399520</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.6978027736053376</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5573880</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2459000</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.44116486181977366</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1666195</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.32248727427564983</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>298535.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.7780730446900345E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10740580</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4125195</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.38407562720076571</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B914B260-76A6-4468-8847-C732969CD1A1}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9">
-        <v>45919</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1">
-        <v>1292.72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E2" s="8">
-        <f>(E1-E13)/E13</f>
-        <v>-6.9572208221878426E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1752300</v>
-      </c>
-      <c r="C4" s="7">
-        <v>-863680</v>
-      </c>
-      <c r="D4" s="5">
-        <f>C4/B4</f>
-        <v>-0.49288363864635049</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3249040</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-1195800</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C5/B5</f>
-        <v>-0.36804717701228673</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7">
-        <v>572540</v>
-      </c>
-      <c r="C6" s="7">
-        <v>-399520</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C6/B6</f>
-        <v>-0.6978027736053376</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6">
-        <f>SUM(B4:B6)</f>
-        <v>5573880</v>
-      </c>
-      <c r="C7" s="6">
-        <f>SUM(C4:C6)</f>
-        <v>-2459000</v>
-      </c>
-      <c r="D7" s="5">
-        <f>C7/B7</f>
-        <v>-0.44116486181977366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5166700</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1666195</v>
-      </c>
-      <c r="D9" s="5">
-        <f>C9/B9</f>
-        <v>-0.32248727427564983</v>
-      </c>
-      <c r="E9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
-        <v>298535.7</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10/B9</f>
-        <v>5.7780730446900345E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B7+B9</f>
-        <v>10740580</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C7+C9</f>
-        <v>-4125195</v>
-      </c>
-      <c r="D11" s="5">
-        <f>C11/B11</f>
-        <v>-0.38407562720076571</v>
-      </c>
-      <c r="E11">
-        <f>E4+E5+E6+E9</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>45912</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1293.6199999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>4</v>
-      </c>
-      <c r="B16" s="7">
-        <v>300140</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-200500</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.66802158992470184</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>3</v>
-      </c>
-      <c r="B17" s="7">
-        <v>3588400</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1226640</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.34183480102552671</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1543740</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-952600</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.61707282314379364</v>
-      </c>
-      <c r="E18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>5432280</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2379740</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.43807388426222504</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5128200</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1671190</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.3258823758823759</v>
-      </c>
-      <c r="E21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
-        <v>295995.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.7719219219219221E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6">
-        <v>10560480</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4050930</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.38359335939275485</v>
-      </c>
-      <c r="E23">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>